--- a/ru/downloads/data-excel/5.4.1.xlsx
+++ b/ru/downloads/data-excel/5.4.1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -542,14 +542,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="41.42578125" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -571,14 +571,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-    </row>
-    <row r="4" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>18</v>
       </c>
@@ -594,8 +595,11 @@
       <c r="E4" s="6">
         <v>2020</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F4" s="6">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -611,8 +615,11 @@
       <c r="E5" s="8">
         <v>11.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F5" s="8">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
@@ -628,8 +635,11 @@
       <c r="E6" s="3">
         <v>10.7</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F6" s="3">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
@@ -645,8 +655,11 @@
       <c r="E7" s="3">
         <v>11.9</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F7" s="3">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>27</v>
       </c>
@@ -662,8 +675,11 @@
       <c r="E8" s="3">
         <v>3.9</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F8" s="3">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
@@ -679,8 +695,11 @@
       <c r="E9" s="3">
         <v>18.100000000000001</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F9" s="3">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>9</v>
       </c>
@@ -696,8 +715,11 @@
       <c r="E10" s="8">
         <v>2.6</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F10" s="8">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>21</v>
       </c>
@@ -713,8 +735,11 @@
       <c r="E11" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F11" s="3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>24</v>
       </c>
@@ -730,8 +755,11 @@
       <c r="E12" s="3">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F12" s="3">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>27</v>
       </c>
@@ -747,8 +775,11 @@
       <c r="E13" s="3">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F13" s="3">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>30</v>
       </c>
@@ -764,8 +795,11 @@
       <c r="E14" s="3">
         <v>1.7</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F14" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>12</v>
       </c>
@@ -781,8 +815,11 @@
       <c r="E15" s="11">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F15" s="11">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
@@ -798,8 +835,11 @@
       <c r="E16" s="7">
         <v>1.7</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F16" s="7">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>24</v>
       </c>
@@ -815,8 +855,11 @@
       <c r="E17" s="7">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F17" s="7">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>27</v>
       </c>
@@ -832,8 +875,11 @@
       <c r="E18" s="7">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F18" s="7">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>30</v>
       </c>
@@ -849,8 +895,11 @@
       <c r="E19" s="7">
         <v>2.8</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F19" s="7">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>15</v>
       </c>
@@ -866,8 +915,11 @@
       <c r="E20" s="12">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F20" s="8">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>21</v>
       </c>
@@ -883,8 +935,11 @@
       <c r="E21" s="13">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F21" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>24</v>
       </c>
@@ -900,8 +955,11 @@
       <c r="E22" s="13">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F22" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>27</v>
       </c>
@@ -917,8 +975,11 @@
       <c r="E23" s="13">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F23" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>30</v>
       </c>
@@ -932,6 +993,9 @@
         <v>0.3</v>
       </c>
       <c r="E24" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="F24" s="5">
         <v>0.3</v>
       </c>
     </row>
